--- a/data/trans_camb/P20-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P20-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,73</t>
+          <t>1,93; 6,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,92</t>
+          <t>0,86; 4,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,87</t>
+          <t>2,34; 6,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,94</t>
+          <t>0,75; 7,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 2,64</t>
+          <t>-2,77; 2,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 1,81</t>
+          <t>-3,18; 1,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 6,09</t>
+          <t>2,15; 5,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 3,22</t>
+          <t>-0,3; 3,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,72</t>
+          <t>0,26; 3,61</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54,24; 368,82</t>
+          <t>54,31; 353,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,65; 280,1</t>
+          <t>25,22; 283,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,56; 382,59</t>
+          <t>63,44; 380,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,89; 126,12</t>
+          <t>7,76; 128,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,36; 47,4</t>
+          <t>-35,64; 52,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,65; 35,47</t>
+          <t>-39,13; 33,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,36; 158,11</t>
+          <t>37,74; 147,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 81,57</t>
+          <t>-3,56; 83,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,97; 93,36</t>
+          <t>4,42; 94,49</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 4,15</t>
+          <t>0,13; 4,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,34</t>
+          <t>-1,22; 2,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 2,12</t>
+          <t>-2,3; 2,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 3,94</t>
+          <t>-0,82; 4,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 1,82</t>
+          <t>-2,89; 1,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 1,14</t>
+          <t>-3,33; 1,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 3,45</t>
+          <t>0,28; 3,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,62</t>
+          <t>-1,38; 1,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 0,94</t>
+          <t>-2,72; 1,06</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 139,43</t>
+          <t>1,92; 133,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 79,83</t>
+          <t>-27,69; 82,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,53; 64,92</t>
+          <t>-49,03; 67,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 62,62</t>
+          <t>-9,59; 68,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,51; 28,72</t>
+          <t>-32,54; 30,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 18,42</t>
+          <t>-37,3; 19,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 69,17</t>
+          <t>4,02; 72,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,88; 32,16</t>
+          <t>-20,97; 30,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-43,81; 18,78</t>
+          <t>-42,21; 20,35</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 3,58</t>
+          <t>-2,07; 3,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 1,28</t>
+          <t>-3,54; 1,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,7</t>
+          <t>-3,01; 1,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 4,22</t>
+          <t>-1,71; 4,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 1,37</t>
+          <t>-4,31; 1,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,79; -1,91</t>
+          <t>-7,43; -1,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,98</t>
+          <t>-0,94; 3,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 0,51</t>
+          <t>-3,41; 0,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,74; -0,83</t>
+          <t>-4,89; -0,79</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,9; 81,93</t>
+          <t>-30,19; 77,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-52,36; 32,34</t>
+          <t>-54,22; 32,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,77; 38,18</t>
+          <t>-43,67; 46,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 62,01</t>
+          <t>-18,27; 62,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,24; 19,45</t>
+          <t>-43,06; 22,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-76,03; -26,31</t>
+          <t>-75,95; -25,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 50,39</t>
+          <t>-12,89; 53,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-38,02; 9,14</t>
+          <t>-40,69; 10,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-61,24; -14,23</t>
+          <t>-59,92; -12,73</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,11</t>
+          <t>-0,91; 2,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 2,44</t>
+          <t>-1,27; 2,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 4,13</t>
+          <t>0,03; 3,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 4,49</t>
+          <t>-0,38; 4,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 4,79</t>
+          <t>0,19; 4,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,73</t>
+          <t>-2,36; 1,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 3,02</t>
+          <t>0,04; 3,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 3,21</t>
+          <t>0,07; 3,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 2,44</t>
+          <t>-0,84; 2,21</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 81,88</t>
+          <t>-18,06; 79,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-24,75; 66,13</t>
+          <t>-23,44; 69,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 109,93</t>
+          <t>-0,15; 102,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 80,4</t>
+          <t>-4,88; 77,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,27; 84,96</t>
+          <t>2,44; 84,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-28,04; 31,63</t>
+          <t>-29,53; 33,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 59,97</t>
+          <t>0,55; 63,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 65,35</t>
+          <t>0,58; 65,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 50,14</t>
+          <t>-12,84; 44,74</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,08</t>
+          <t>0,87; 3,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,74</t>
+          <t>-0,37; 1,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,46</t>
+          <t>-0,13; 2,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,46</t>
+          <t>0,83; 3,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,71</t>
+          <t>-0,92; 1,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,82; -0,18</t>
+          <t>-2,82; -0,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,92</t>
+          <t>1,08; 2,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,42</t>
+          <t>-0,34; 1,29</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,79</t>
+          <t>-1,12; 0,8</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>18,03; 85,72</t>
+          <t>19,09; 86,84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 47,99</t>
+          <t>-8,53; 45,19</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2,06; 66,53</t>
+          <t>-2,29; 66,86</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9,42; 51,69</t>
+          <t>10,13; 52,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 25,69</t>
+          <t>-11,09; 23,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-35,19; -2,68</t>
+          <t>-36,1; -2,96</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,84; 54,66</t>
+          <t>17,48; 55,9</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 27,01</t>
+          <t>-5,43; 23,72</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-16,12; 14,32</t>
+          <t>-18,15; 14,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P20-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P20-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,49</t>
+          <t>4,45</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,6</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,94</t>
+          <t>2,0</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,39</t>
+          <t>1,99; 6,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,94</t>
+          <t>0,91; 5,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 6,79</t>
+          <t>2,3; 6,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,13</t>
+          <t>0,81; 7,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 2,77</t>
+          <t>-2,73; 2,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 1,9</t>
+          <t>-3,02; 2,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,95</t>
+          <t>2,25; 6,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 3,28</t>
+          <t>-0,17; 3,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,61</t>
+          <t>0,46; 3,63</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>180,29%</t>
+          <t>178,63%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-8,82%</t>
+          <t>-6,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>42,85%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54,31; 353,36</t>
+          <t>60,29; 381,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,22; 283,0</t>
+          <t>22,58; 288,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,44; 380,57</t>
+          <t>62,37; 416,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,76; 128,87</t>
+          <t>9,11; 134,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,64; 52,22</t>
+          <t>-34,05; 52,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,13; 33,42</t>
+          <t>-37,25; 39,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,74; 147,81</t>
+          <t>39,24; 156,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 83,01</t>
+          <t>-3,51; 82,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,42; 94,49</t>
+          <t>8,78; 93,81</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>1,33</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,16</t>
+          <t>-1,27</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,68</t>
+          <t>0,03</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 4,08</t>
+          <t>0,34; 4,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,34</t>
+          <t>-1,19; 2,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 2,16</t>
+          <t>-0,5; 3,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 4,28</t>
+          <t>-1,03; 4,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 1,98</t>
+          <t>-2,72; 2,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 1,28</t>
+          <t>-3,6; 1,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,66</t>
+          <t>0,25; 3,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,53</t>
+          <t>-1,41; 1,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 1,06</t>
+          <t>-1,67; 1,45</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-14,98%</t>
+          <t>-16,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-11,66%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 133,98</t>
+          <t>3,7; 136,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,69; 82,27</t>
+          <t>-24,57; 72,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,03; 67,35</t>
+          <t>-11,2; 118,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 68,31</t>
+          <t>-11,84; 60,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,54; 30,26</t>
+          <t>-30,49; 31,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,3; 19,32</t>
+          <t>-40,05; 16,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,02; 72,55</t>
+          <t>3,05; 68,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,97; 30,55</t>
+          <t>-21,99; 32,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-42,21; 20,35</t>
+          <t>-24,56; 28,55</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>-0,84</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,27</t>
+          <t>-2,3</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,48</t>
+          <t>-1,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 3,38</t>
+          <t>-1,89; 3,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 1,31</t>
+          <t>-3,68; 1,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,97</t>
+          <t>-3,28; 1,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 4,53</t>
+          <t>-1,62; 4,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 1,48</t>
+          <t>-4,11; 1,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,43; -1,79</t>
+          <t>-5,12; 0,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 3,14</t>
+          <t>-1,03; 3,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 0,57</t>
+          <t>-3,1; 0,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,89; -0,79</t>
+          <t>-3,38; 0,14</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-10,01%</t>
+          <t>-15,11%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-50,64%</t>
+          <t>-27,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-35,37%</t>
+          <t>-22,47%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,19; 77,95</t>
+          <t>-28,11; 78,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-54,22; 32,75</t>
+          <t>-54,63; 24,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-43,67; 46,03</t>
+          <t>-47,36; 38,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 62,22</t>
+          <t>-17,26; 61,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,06; 22,07</t>
+          <t>-41,27; 21,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-75,95; -25,31</t>
+          <t>-50,35; 5,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 53,15</t>
+          <t>-12,74; 51,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-40,69; 10,44</t>
+          <t>-38,98; 12,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-59,92; -12,73</t>
+          <t>-42,69; 2,34</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>1,96</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>1,15</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,95</t>
+          <t>-0,95; 3,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 2,54</t>
+          <t>-1,58; 2,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,03; 3,87</t>
+          <t>-0,02; 3,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 4,23</t>
+          <t>-0,37; 4,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 4,87</t>
+          <t>-0,25; 4,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 1,88</t>
+          <t>-2,0; 2,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 3,07</t>
+          <t>0,02; 3,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 3,27</t>
+          <t>0,03; 3,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,21</t>
+          <t>-0,41; 2,59</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-0,52%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 79,25</t>
+          <t>-17,46; 89,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,44; 69,57</t>
+          <t>-28,64; 66,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 102,65</t>
+          <t>-0,68; 102,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 77,12</t>
+          <t>-4,93; 74,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,44; 84,85</t>
+          <t>-3,95; 85,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-29,53; 33,82</t>
+          <t>-25,12; 40,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,55; 63,02</t>
+          <t>0,1; 61,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,58; 65,56</t>
+          <t>-0,76; 64,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 44,74</t>
+          <t>-6,32; 52,28</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,67</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>-0,81</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>0,42</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,07</t>
+          <t>0,84; 3,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,67</t>
+          <t>-0,33; 1,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 2,44</t>
+          <t>0,67; 2,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,51</t>
+          <t>0,87; 3,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,56</t>
+          <t>-0,91; 1,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,82; -0,21</t>
+          <t>-2,1; 0,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,94</t>
+          <t>1,12; 2,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,29</t>
+          <t>-0,3; 1,39</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,8</t>
+          <t>-0,33; 1,23</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-19,7%</t>
+          <t>-10,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-1,64%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>19,09; 86,84</t>
+          <t>17,44; 84,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 45,19</t>
+          <t>-7,04; 45,94</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 66,86</t>
+          <t>14,11; 77,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10,13; 52,15</t>
+          <t>11,11; 54,14</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 23,3</t>
+          <t>-11,37; 24,42</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,1; -2,96</t>
+          <t>-25,7; 5,75</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,48; 55,9</t>
+          <t>17,64; 53,73</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 23,72</t>
+          <t>-5,09; 25,84</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 14,83</t>
+          <t>-5,07; 23,79</t>
         </is>
       </c>
     </row>
